--- a/data/trans_camb/IP1013-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,36</t>
+          <t>-0,88; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-2,51; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,95</t>
+          <t>-0,46; 1,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,87</t>
+          <t>-0,46; 1,09</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,68</t>
+          <t>-1,61; 0,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,0</t>
+          <t>-2,28; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,64</t>
+          <t>-0,62; 0,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,0</t>
+          <t>-1,08; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,6</t>
+          <t>-0,27; 0,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,52</t>
+          <t>-0,29; 0,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,54</t>
+          <t>-0,1; 0,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 779,25</t>
+          <t>-69,36; 1067,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Habitat-trans_camb.xlsx
@@ -631,22 +631,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,35</t>
+          <t>-0,9; 1,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,0</t>
+          <t>-2,19; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,09</t>
+          <t>-0,46; 0,84</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,67</t>
+          <t>-1,61; 0,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,0</t>
+          <t>-1,25; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,52</t>
+          <t>-0,27; 0,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,61</t>
+          <t>-0,1; 0,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,56; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,43</t>
+          <t>-0,09; 0,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,24</t>
+          <t>-0,22; 0,25</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-69,36; 1067,2</t>
+          <t>-66,5; inf</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,58</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>-1,3; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>-2,17; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,38</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,0</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,16</t>
+          <t>-0,46; 0,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,84</t>
+          <t>-0,46; 0,87</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,68</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>-1,45; 0,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,25; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,64</t>
+          <t>-0,47; 0,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,0</t>
+          <t>-1,09; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-48,51%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,63</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,11</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,6</t>
+          <t>-0,11; 0,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,56</t>
+          <t>-0,47; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,54</t>
+          <t>-0,26; 0,6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,0</t>
+          <t>-0,27; 0,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,43</t>
+          <t>-0,1; 0,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,25</t>
+          <t>-0,23; 0,24</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>183,98%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>58,24%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>58,61%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>183,98%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-66,5; inf</t>
+          <t>-79,12; 779,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
